--- a/docs/verification/files/rocscience/joints/rj004.xlsx
+++ b/docs/verification/files/rocscience/joints/rj004.xlsx
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
+        <v>132.0790560447</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>

--- a/docs/verification/files/rocscience/joints/rj004.xlsx
+++ b/docs/verification/files/rocscience/joints/rj004.xlsx
@@ -3454,7 +3454,11 @@
       <c r="C23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
